--- a/CHEQUES NUEVO.xlsx
+++ b/CHEQUES NUEVO.xlsx
@@ -1,37 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30306"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D8EB1F4-1E21-4E34-BF92-C173C1946ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\sistema_imprenta_datos\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59566DE0-562A-4984-BD95-F39DD16DB179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>NEA</t>
   </si>
@@ -57,27 +46,6 @@
     <t>HIERROS LIDER</t>
   </si>
   <si>
-    <t>$159602 (18/11)</t>
-  </si>
-  <si>
-    <t>$600000 23/11</t>
-  </si>
-  <si>
-    <t>$200000 (04/12)</t>
-  </si>
-  <si>
-    <t>$229500 (08/12)</t>
-  </si>
-  <si>
-    <t>$369308 (12/12)</t>
-  </si>
-  <si>
-    <t>$200000 (18/12)</t>
-  </si>
-  <si>
-    <t>$209865 (30/12)</t>
-  </si>
-  <si>
     <t>$340246 (05/01)</t>
   </si>
   <si>
@@ -181,13 +149,28 @@
   </si>
   <si>
     <t>$320552 (25/08)</t>
+  </si>
+  <si>
+    <t>$265000.0 31/08</t>
+  </si>
+  <si>
+    <t>$265000.0 15/09</t>
+  </si>
+  <si>
+    <t>$265000.0 30/09</t>
+  </si>
+  <si>
+    <t>$350000.0 10/10</t>
+  </si>
+  <si>
+    <t>$398200.0 10/11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,7 +179,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,6 +198,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -228,11 +223,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -567,8 +563,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
     <col min="2" max="3" width="18.7109375" customWidth="1"/>
@@ -579,7 +575,7 @@
     <col min="8" max="8" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -605,215 +601,205 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="D3" s="2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="D6" s="1" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="D10" s="1" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="B13" s="1" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E13" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
       <c r="B16" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="B17" s="1" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="E18" s="1" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="B19" s="1" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C19" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="E20" s="1" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="B21" s="1" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E22" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3"/>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="E24" s="1" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C26" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F27" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E28" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="E29" s="1" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C29" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="B30" s="1" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F30" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="B31" s="1" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E31" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="B32" s="1" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E32" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="3:8">
-      <c r="C33" s="1" t="s">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G33" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="3:8">
-      <c r="F34" s="1" t="s">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H34" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="3:8">
-      <c r="E35" s="1" t="s">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G35" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="3:8">
-      <c r="C36" s="1" t="s">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G36" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="3:8">
-      <c r="F37" s="1" t="s">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="3:8">
-      <c r="E38" s="1" t="s">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="3:8">
-      <c r="E39" s="1" t="s">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="3:8">
-      <c r="G40" t="s">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="3:8">
-      <c r="H41" t="s">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="3:8">
-      <c r="G42" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="43" spans="3:8">
-      <c r="G43" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/CHEQUES NUEVO.xlsx
+++ b/CHEQUES NUEVO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\sistema_imprenta_datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59566DE0-562A-4984-BD95-F39DD16DB179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4F6CE2-AA60-431B-9437-51D3FAEF3721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -778,7 +778,7 @@
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>43</v>
       </c>
     </row>
